--- a/data/trans_orig/POLIPATOLOGIA_Lim_2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_Lim_2-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2012</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32297</t>
+          <t>31707</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56286</t>
+          <t>57156</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69410</t>
+          <t>71192</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>102145</t>
+          <t>103579</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>110331</t>
+          <t>108566</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>152997</t>
+          <t>150064</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>238452</t>
+          <t>237582</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>262441</t>
+          <t>263031</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>185100</t>
+          <t>183666</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>217835</t>
+          <t>216053</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>428986</t>
+          <t>431919</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>471652</t>
+          <t>473417</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,35%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75200</t>
+          <t>76573</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>114620</t>
+          <t>114825</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136969</t>
+          <t>136461</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>179451</t>
+          <t>180171</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>219749</t>
+          <t>222987</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>280326</t>
+          <t>281173</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>390907</t>
+          <t>390702</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>430327</t>
+          <t>428954</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>344314</t>
+          <t>343594</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>386796</t>
+          <t>387304</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>748966</t>
+          <t>748119</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>809543</t>
+          <t>806305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,34%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53529</t>
+          <t>53004</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83438</t>
+          <t>82550</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74486</t>
+          <t>74109</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109274</t>
+          <t>108499</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>137232</t>
+          <t>137608</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181084</t>
+          <t>181706</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>240608</t>
+          <t>241496</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>270517</t>
+          <t>271042</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>231746</t>
+          <t>232521</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>266534</t>
+          <t>266911</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>483982</t>
+          <t>483360</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>527834</t>
+          <t>527458</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,31%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41676</t>
+          <t>42465</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71204</t>
+          <t>71383</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105195</t>
+          <t>104874</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>142193</t>
+          <t>142600</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>155686</t>
+          <t>155805</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>203011</t>
+          <t>202831</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>302778</t>
+          <t>302599</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>332306</t>
+          <t>331517</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>246758</t>
+          <t>246351</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>283756</t>
+          <t>284077</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>559922</t>
+          <t>560102</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>607247</t>
+          <t>607128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,58%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35517</t>
+          <t>35250</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59841</t>
+          <t>60453</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>89225</t>
+          <t>89684</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119737</t>
+          <t>120803</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>130979</t>
+          <t>130164</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>171838</t>
+          <t>172002</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,8%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152777</t>
+          <t>152165</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177101</t>
+          <t>177368</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99854</t>
+          <t>98788</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130366</t>
+          <t>129907</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>260371</t>
+          <t>260207</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>301230</t>
+          <t>302045</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,88%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51143</t>
+          <t>50422</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78600</t>
+          <t>78436</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>77782</t>
+          <t>79829</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>108296</t>
+          <t>112173</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>138612</t>
+          <t>138131</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>181047</t>
+          <t>180246</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,53%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>195381</t>
+          <t>195545</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>222838</t>
+          <t>223559</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>171735</t>
+          <t>167858</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>202249</t>
+          <t>200202</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>372965</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>415400</t>
+          <t>415881</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>86650</t>
+          <t>84679</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125123</t>
+          <t>124668</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>165425</t>
+          <t>164993</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>213605</t>
+          <t>212072</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>265327</t>
+          <t>262474</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>326614</t>
+          <t>326661</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>537665</t>
+          <t>538120</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>576138</t>
+          <t>578109</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>480248</t>
+          <t>481781</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>528428</t>
+          <t>528860</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1030027</t>
+          <t>1029980</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1091314</t>
+          <t>1094167</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>90101</t>
+          <t>89227</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>130469</t>
+          <t>128357</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>166971</t>
+          <t>166911</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>217408</t>
+          <t>216825</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>272970</t>
+          <t>267032</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>336781</t>
+          <t>334373</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>648629</t>
+          <t>650741</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>688997</t>
+          <t>689871</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>606445</t>
+          <t>607028</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>656882</t>
+          <t>656942</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1266170</t>
+          <t>1268578</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1329981</t>
+          <t>1335919</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,34%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>539147</t>
+          <t>538765</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>628616</t>
+          <t>628083</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>985463</t>
+          <t>990630</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1095935</t>
+          <t>1099426</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1547932</t>
+          <t>1554153</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1698386</t>
+          <t>1693328</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2798163</t>
+          <t>2798696</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2887632</t>
+          <t>2888014</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2462374</t>
+          <t>2458883</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2572846</t>
+          <t>2567679</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5286702</t>
+          <t>5291760</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5437156</t>
+          <t>5430935</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,75%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2016</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31265</t>
+          <t>30889</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55926</t>
+          <t>57782</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77036</t>
+          <t>76466</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>108101</t>
+          <t>109352</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>115733</t>
+          <t>113991</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158505</t>
+          <t>156010</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>237835</t>
+          <t>235979</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>262496</t>
+          <t>262872</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>180602</t>
+          <t>179351</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>211667</t>
+          <t>212237</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>423959</t>
+          <t>426454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>466731</t>
+          <t>468473</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,43%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53086</t>
+          <t>52945</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81917</t>
+          <t>84595</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>119659</t>
+          <t>120784</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>161949</t>
+          <t>161433</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>179007</t>
+          <t>181722</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>233401</t>
+          <t>233748</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>420658</t>
+          <t>417980</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>449489</t>
+          <t>449630</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>361135</t>
+          <t>361651</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>403425</t>
+          <t>402300</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>792258</t>
+          <t>791911</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>846652</t>
+          <t>843937</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,28%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28189</t>
+          <t>28348</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49975</t>
+          <t>50102</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61635</t>
+          <t>62889</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93185</t>
+          <t>94087</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97668</t>
+          <t>95005</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135596</t>
+          <t>134126</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>268590</t>
+          <t>268463</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>290376</t>
+          <t>290217</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>243124</t>
+          <t>242222</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>274674</t>
+          <t>273420</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>519278</t>
+          <t>520748</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>557206</t>
+          <t>559869</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,49%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48685</t>
+          <t>48293</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76387</t>
+          <t>76816</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>101434</t>
+          <t>101524</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141064</t>
+          <t>141854</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157048</t>
+          <t>159627</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>209032</t>
+          <t>210729</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293577</t>
+          <t>293148</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>321279</t>
+          <t>321671</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>246219</t>
+          <t>245429</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>285849</t>
+          <t>285759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>548215</t>
+          <t>546518</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>600199</t>
+          <t>597620</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>78,92%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22449</t>
+          <t>22470</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43372</t>
+          <t>43868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51795</t>
+          <t>51083</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77559</t>
+          <t>77842</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>80500</t>
+          <t>80641</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113243</t>
+          <t>114916</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167849</t>
+          <t>167353</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>188772</t>
+          <t>188751</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>141028</t>
+          <t>140745</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>166792</t>
+          <t>167504</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>316565</t>
+          <t>314892</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>349308</t>
+          <t>349167</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,24%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37511</t>
+          <t>37071</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63039</t>
+          <t>62288</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58000</t>
+          <t>60230</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88931</t>
+          <t>89281</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>103350</t>
+          <t>104903</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>144796</t>
+          <t>145251</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200084</t>
+          <t>200835</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>225612</t>
+          <t>226052</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>184184</t>
+          <t>183834</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>215115</t>
+          <t>212885</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>391442</t>
+          <t>390987</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>432888</t>
+          <t>431335</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,44%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>74435</t>
+          <t>74709</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>113322</t>
+          <t>111214</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>126984</t>
+          <t>125856</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>172799</t>
+          <t>170438</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>213134</t>
+          <t>214184</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>273504</t>
+          <t>272580</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>543236</t>
+          <t>545344</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>582123</t>
+          <t>581849</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>518495</t>
+          <t>520856</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>564310</t>
+          <t>565438</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1074348</t>
+          <t>1075272</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1134718</t>
+          <t>1133668</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,11%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>103385</t>
+          <t>104065</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>146120</t>
+          <t>144283</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>170739</t>
+          <t>174121</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>224375</t>
+          <t>225072</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>292000</t>
+          <t>288975</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>357444</t>
+          <t>356937</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>632463</t>
+          <t>634300</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>675198</t>
+          <t>674518</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>601792</t>
+          <t>601095</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>655428</t>
+          <t>652046</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1247306</t>
+          <t>1247813</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1312750</t>
+          <t>1315775</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>465684</t>
+          <t>464515</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>548403</t>
+          <t>548687</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>858554</t>
+          <t>860858</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>967781</t>
+          <t>968200</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1346697</t>
+          <t>1344647</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1488780</t>
+          <t>1484176</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2845947</t>
+          <t>2845663</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2928666</t>
+          <t>2929835</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2576761</t>
+          <t>2576342</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2685988</t>
+          <t>2683684</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5450112</t>
+          <t>5454716</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5592195</t>
+          <t>5594245</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,62%</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2023</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35585</t>
+          <t>36797</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63178</t>
+          <t>61685</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60464</t>
+          <t>60192</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82284</t>
+          <t>82654</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101446</t>
+          <t>104158</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136831</t>
+          <t>138673</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>248265</t>
+          <t>249758</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>275858</t>
+          <t>274646</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>207351</t>
+          <t>206981</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>229171</t>
+          <t>229443</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>464246</t>
+          <t>462404</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>499631</t>
+          <t>496919</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58404</t>
+          <t>58885</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91759</t>
+          <t>93574</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>140062</t>
+          <t>142427</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>176484</t>
+          <t>177653</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>207397</t>
+          <t>206624</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>261163</t>
+          <t>258822</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>426631</t>
+          <t>424816</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>459986</t>
+          <t>459505</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>338485</t>
+          <t>337316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>374907</t>
+          <t>372542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>772196</t>
+          <t>774537</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>825962</t>
+          <t>826735</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,0%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60871</t>
+          <t>60836</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88857</t>
+          <t>87465</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101324</t>
+          <t>101860</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130999</t>
+          <t>128478</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>170342</t>
+          <t>170055</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>210626</t>
+          <t>210048</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>227193</t>
+          <t>228585</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>255179</t>
+          <t>255214</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218129</t>
+          <t>220650</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>247804</t>
+          <t>247268</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>454552</t>
+          <t>455130</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>494836</t>
+          <t>495123</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,43%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64239</t>
+          <t>63722</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98499</t>
+          <t>98051</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79684</t>
+          <t>80425</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165696</t>
+          <t>167832</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>156758</t>
+          <t>142872</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>245904</t>
+          <t>242785</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,8%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214058</t>
+          <t>214506</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>248318</t>
+          <t>248835</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>310022</t>
+          <t>307886</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>396034</t>
+          <t>395293</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>542370</t>
+          <t>545489</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>631516</t>
+          <t>645402</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>81,88%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18170</t>
+          <t>17850</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32769</t>
+          <t>31663</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29117</t>
+          <t>31350</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75702</t>
+          <t>75815</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53595</t>
+          <t>58017</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98796</t>
+          <t>99806</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>145973</t>
+          <t>147079</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>160572</t>
+          <t>160892</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>183077</t>
+          <t>182964</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>229662</t>
+          <t>227429</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>338725</t>
+          <t>337715</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>383926</t>
+          <t>379504</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>86,74%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57502</t>
+          <t>57024</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80976</t>
+          <t>79998</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>84678</t>
+          <t>84296</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>108679</t>
+          <t>107811</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>147190</t>
+          <t>147611</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>181832</t>
+          <t>180938</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>188660</t>
+          <t>189638</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>212134</t>
+          <t>212612</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>148377</t>
+          <t>149245</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>172378</t>
+          <t>172760</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>344860</t>
+          <t>345754</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>379502</t>
+          <t>379081</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,97%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>118243</t>
+          <t>118333</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>166317</t>
+          <t>163599</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>152100</t>
+          <t>133156</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>381542</t>
+          <t>382248</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>263846</t>
+          <t>273716</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>503668</t>
+          <t>506079</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>457962</t>
+          <t>460680</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>506036</t>
+          <t>505946</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>467723</t>
+          <t>467017</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>697165</t>
+          <t>716109</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>969876</t>
+          <t>967465</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1209698</t>
+          <t>1199828</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,42%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36918</t>
+          <t>39547</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>123773</t>
+          <t>124649</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>168716</t>
+          <t>169700</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>208603</t>
+          <t>209324</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>169348</t>
+          <t>171320</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>330763</t>
+          <t>332537</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>804947</t>
+          <t>804071</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>891802</t>
+          <t>889173</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>509128</t>
+          <t>508407</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>549015</t>
+          <t>548031</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1315689</t>
+          <t>1313915</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1477104</t>
+          <t>1475132</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,59%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>470623</t>
+          <t>457566</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>656562</t>
+          <t>659443</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>895754</t>
+          <t>872848</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1194646</t>
+          <t>1194874</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1456828</t>
+          <t>1444766</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1814962</t>
+          <t>1814112</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2803255</t>
+          <t>2800374</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2989194</t>
+          <t>3002251</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2517634</t>
+          <t>2517406</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2816526</t>
+          <t>2839432</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5357135</t>
+          <t>5357985</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5715269</t>
+          <t>5727331</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/POLIPATOLOGIA_Lim_2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_Lim_2-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31707</t>
+          <t>31631</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57156</t>
+          <t>56326</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71192</t>
+          <t>69227</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>103579</t>
+          <t>103028</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>108566</t>
+          <t>108886</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>150064</t>
+          <t>151265</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>237582</t>
+          <t>238412</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>263031</t>
+          <t>263107</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>183666</t>
+          <t>184217</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>216053</t>
+          <t>218018</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>431919</t>
+          <t>430718</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>473417</t>
+          <t>473097</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,29%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76573</t>
+          <t>72621</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>114825</t>
+          <t>111821</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136461</t>
+          <t>134312</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>180171</t>
+          <t>179449</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>222987</t>
+          <t>220126</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>281173</t>
+          <t>282699</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>390702</t>
+          <t>393706</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>428954</t>
+          <t>432906</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>343594</t>
+          <t>344316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>387304</t>
+          <t>389453</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>748119</t>
+          <t>746593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>806305</t>
+          <t>809166</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,61%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53004</t>
+          <t>53066</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82550</t>
+          <t>83441</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74109</t>
+          <t>73147</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108499</t>
+          <t>106545</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>137608</t>
+          <t>135718</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181706</t>
+          <t>180967</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>241496</t>
+          <t>240605</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>271042</t>
+          <t>270980</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>232521</t>
+          <t>234475</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>266911</t>
+          <t>267873</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>483360</t>
+          <t>484099</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>527458</t>
+          <t>529348</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,59%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42465</t>
+          <t>43281</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71383</t>
+          <t>71429</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>104874</t>
+          <t>106733</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>142600</t>
+          <t>141316</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>155805</t>
+          <t>156428</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>202831</t>
+          <t>203558</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>302599</t>
+          <t>302553</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>331517</t>
+          <t>330701</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>246351</t>
+          <t>247635</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>284077</t>
+          <t>282218</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>560102</t>
+          <t>559375</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>607128</t>
+          <t>606505</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,5%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35250</t>
+          <t>34577</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60453</t>
+          <t>60108</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>89684</t>
+          <t>88610</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>120803</t>
+          <t>116305</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>130164</t>
+          <t>129168</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172002</t>
+          <t>170762</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152165</t>
+          <t>152510</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177368</t>
+          <t>178041</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98788</t>
+          <t>103286</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129907</t>
+          <t>130981</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>260207</t>
+          <t>261447</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>302045</t>
+          <t>303041</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>70,11%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50422</t>
+          <t>51510</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78436</t>
+          <t>79684</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79829</t>
+          <t>79112</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112173</t>
+          <t>109914</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>138131</t>
+          <t>135494</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>180246</t>
+          <t>178322</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>195545</t>
+          <t>194297</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223559</t>
+          <t>222471</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>167858</t>
+          <t>170117</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>200202</t>
+          <t>200919</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>373766</t>
+          <t>375690</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>415881</t>
+          <t>418518</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,54%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84679</t>
+          <t>85002</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>124668</t>
+          <t>124969</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>164993</t>
+          <t>166763</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>212072</t>
+          <t>215563</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>262474</t>
+          <t>264798</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>326661</t>
+          <t>325334</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>538120</t>
+          <t>537819</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>578109</t>
+          <t>577786</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>481781</t>
+          <t>478290</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>528860</t>
+          <t>527090</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1029980</t>
+          <t>1031307</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1094167</t>
+          <t>1091843</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,48%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>89227</t>
+          <t>88676</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>128357</t>
+          <t>129482</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>168589</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>216825</t>
+          <t>219985</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>267032</t>
+          <t>273161</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>334373</t>
+          <t>336610</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>650741</t>
+          <t>649616</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>689871</t>
+          <t>690422</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>607028</t>
+          <t>603868</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>656942</t>
+          <t>655264</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1268578</t>
+          <t>1266341</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1335919</t>
+          <t>1329790</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,96%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>538765</t>
+          <t>536420</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>628083</t>
+          <t>633209</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>990630</t>
+          <t>987012</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1099426</t>
+          <t>1089080</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1554153</t>
+          <t>1545276</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1693328</t>
+          <t>1696504</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2798696</t>
+          <t>2793570</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2888014</t>
+          <t>2890359</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2458883</t>
+          <t>2469229</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2567679</t>
+          <t>2571297</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5291760</t>
+          <t>5288584</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5430935</t>
+          <t>5439812</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,88%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30889</t>
+          <t>31074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57782</t>
+          <t>56075</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76466</t>
+          <t>75096</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>109352</t>
+          <t>108559</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>113991</t>
+          <t>112433</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>156010</t>
+          <t>154804</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>235979</t>
+          <t>237686</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>262872</t>
+          <t>262687</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>179351</t>
+          <t>180144</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>212237</t>
+          <t>213607</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>426454</t>
+          <t>427660</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>468473</t>
+          <t>470031</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,7%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52945</t>
+          <t>52582</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84595</t>
+          <t>84329</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>120784</t>
+          <t>120533</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>161433</t>
+          <t>162032</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>181722</t>
+          <t>180655</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>233748</t>
+          <t>235468</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>417980</t>
+          <t>418246</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>449630</t>
+          <t>449993</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>361651</t>
+          <t>361052</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>402300</t>
+          <t>402551</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>791911</t>
+          <t>790191</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>843937</t>
+          <t>845004</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28348</t>
+          <t>27683</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50102</t>
+          <t>48587</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62889</t>
+          <t>62601</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94087</t>
+          <t>96725</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95005</t>
+          <t>97551</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>134126</t>
+          <t>136656</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>268463</t>
+          <t>269978</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>290217</t>
+          <t>290882</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>242222</t>
+          <t>239584</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>273420</t>
+          <t>273708</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>520748</t>
+          <t>518218</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>559869</t>
+          <t>557323</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,1%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48293</t>
+          <t>47417</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76816</t>
+          <t>75919</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>101524</t>
+          <t>101657</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141854</t>
+          <t>140203</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>159627</t>
+          <t>158408</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>210729</t>
+          <t>208484</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293148</t>
+          <t>294045</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>321671</t>
+          <t>322547</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>245429</t>
+          <t>247080</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>285759</t>
+          <t>285626</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>546518</t>
+          <t>548763</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>597620</t>
+          <t>598839</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,08%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22470</t>
+          <t>23002</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43868</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51083</t>
+          <t>51439</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77842</t>
+          <t>78324</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>80641</t>
+          <t>80158</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114916</t>
+          <t>113283</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167353</t>
+          <t>168091</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>188751</t>
+          <t>188219</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140745</t>
+          <t>140263</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>167504</t>
+          <t>167148</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>314892</t>
+          <t>316525</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>349167</t>
+          <t>349650</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,35%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37071</t>
+          <t>36982</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62288</t>
+          <t>62928</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60230</t>
+          <t>59191</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89281</t>
+          <t>89145</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>104903</t>
+          <t>102992</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>145251</t>
+          <t>144002</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200835</t>
+          <t>200195</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>226052</t>
+          <t>226141</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>183834</t>
+          <t>183970</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>212885</t>
+          <t>213924</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>390987</t>
+          <t>392236</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>431335</t>
+          <t>433246</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,79%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>74709</t>
+          <t>74153</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>111214</t>
+          <t>112789</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>125856</t>
+          <t>123816</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>170438</t>
+          <t>169164</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>214184</t>
+          <t>214190</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>272580</t>
+          <t>268796</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>545344</t>
+          <t>543769</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>581849</t>
+          <t>582405</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>520856</t>
+          <t>522130</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>565438</t>
+          <t>567478</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1075272</t>
+          <t>1079056</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1133668</t>
+          <t>1133662</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>104065</t>
+          <t>102940</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>144283</t>
+          <t>147995</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>174121</t>
+          <t>173463</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>225072</t>
+          <t>221260</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>288975</t>
+          <t>289041</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>356937</t>
+          <t>353797</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>634300</t>
+          <t>630588</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>674518</t>
+          <t>675643</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>601095</t>
+          <t>604907</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>652046</t>
+          <t>652704</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1247813</t>
+          <t>1250953</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1315775</t>
+          <t>1315709</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>464515</t>
+          <t>465378</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>548687</t>
+          <t>550763</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>860858</t>
+          <t>858479</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>968200</t>
+          <t>975038</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1344647</t>
+          <t>1352608</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1484176</t>
+          <t>1490115</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2845663</t>
+          <t>2843587</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2929835</t>
+          <t>2928972</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2576342</t>
+          <t>2569504</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2683684</t>
+          <t>2686063</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5454716</t>
+          <t>5448777</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5594245</t>
+          <t>5586284</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,51%</t>
         </is>
       </c>
     </row>
@@ -7373,32 +7373,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>47896</t>
+          <t>49749</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36797</t>
+          <t>37961</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61685</t>
+          <t>62074</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7408,32 +7408,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>71186</t>
+          <t>77050</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60192</t>
+          <t>65457</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82654</t>
+          <t>88233</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7443,32 +7443,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>119082</t>
+          <t>126799</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104158</t>
+          <t>109555</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138673</t>
+          <t>142704</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -7486,32 +7486,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>263547</t>
+          <t>269096</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249758</t>
+          <t>256771</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>274646</t>
+          <t>280884</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7521,32 +7521,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>218449</t>
+          <t>239011</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>206981</t>
+          <t>227828</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>229443</t>
+          <t>250604</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7556,32 +7556,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>481995</t>
+          <t>508107</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>462404</t>
+          <t>492202</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>496919</t>
+          <t>525351</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,74%</t>
         </is>
       </c>
     </row>
@@ -7599,17 +7599,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7634,17 +7634,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7669,17 +7669,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7716,32 +7716,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>74001</t>
+          <t>76427</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58885</t>
+          <t>60021</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93574</t>
+          <t>95397</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7751,32 +7751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>158919</t>
+          <t>167745</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>142427</t>
+          <t>150101</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>177653</t>
+          <t>186764</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7786,32 +7786,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>232919</t>
+          <t>244172</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>206624</t>
+          <t>218338</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>258822</t>
+          <t>273127</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -7829,32 +7829,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>444389</t>
+          <t>454220</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>424816</t>
+          <t>435250</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>459505</t>
+          <t>470626</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7864,32 +7864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>356050</t>
+          <t>378749</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>337316</t>
+          <t>359730</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>372542</t>
+          <t>396393</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7899,32 +7899,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>800440</t>
+          <t>832969</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>774537</t>
+          <t>804014</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>826735</t>
+          <t>858803</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,73%</t>
         </is>
       </c>
     </row>
@@ -7942,17 +7942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7977,17 +7977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8012,17 +8012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8059,32 +8059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>73897</t>
+          <t>73318</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60836</t>
+          <t>60086</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87465</t>
+          <t>87816</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8094,32 +8094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>114958</t>
+          <t>117196</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101860</t>
+          <t>103559</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128478</t>
+          <t>131548</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8129,32 +8129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>188855</t>
+          <t>190514</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>170055</t>
+          <t>171275</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>210048</t>
+          <t>209875</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -8172,32 +8172,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>242153</t>
+          <t>242675</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>228585</t>
+          <t>228177</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>255214</t>
+          <t>255907</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8207,32 +8207,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>234170</t>
+          <t>239185</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>220650</t>
+          <t>224833</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>247268</t>
+          <t>252822</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8242,32 +8242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>476323</t>
+          <t>481861</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>455130</t>
+          <t>462500</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>495123</t>
+          <t>501100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,53%</t>
         </is>
       </c>
     </row>
@@ -8285,17 +8285,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8355,17 +8355,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8402,32 +8402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79180</t>
+          <t>88890</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63722</t>
+          <t>71103</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98051</t>
+          <t>111151</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8437,32 +8437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>130191</t>
+          <t>142965</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80425</t>
+          <t>126068</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167832</t>
+          <t>161888</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8472,32 +8472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>209371</t>
+          <t>231855</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142872</t>
+          <t>205958</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242785</t>
+          <t>257799</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -8515,32 +8515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>233377</t>
+          <t>284255</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214506</t>
+          <t>261994</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>248835</t>
+          <t>302042</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8550,32 +8550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>345527</t>
+          <t>278996</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>307886</t>
+          <t>260073</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>395293</t>
+          <t>295893</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8585,32 +8585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>578903</t>
+          <t>563252</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>545489</t>
+          <t>537308</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>645402</t>
+          <t>589149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>74,1%</t>
         </is>
       </c>
     </row>
@@ -8628,17 +8628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8698,17 +8698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8745,32 +8745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24320</t>
+          <t>26223</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17850</t>
+          <t>19213</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31663</t>
+          <t>33933</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8780,32 +8780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>58868</t>
+          <t>61110</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31350</t>
+          <t>52446</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75815</t>
+          <t>69462</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8815,32 +8815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>83189</t>
+          <t>87332</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58017</t>
+          <t>76559</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99806</t>
+          <t>100592</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -8858,32 +8858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>154422</t>
+          <t>179442</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147079</t>
+          <t>171732</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>160892</t>
+          <t>186452</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8893,32 +8893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>199911</t>
+          <t>167808</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>182964</t>
+          <t>159456</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>227429</t>
+          <t>176472</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8928,32 +8928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>354332</t>
+          <t>347250</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>337715</t>
+          <t>333990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>379504</t>
+          <t>358023</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>82,38%</t>
         </is>
       </c>
     </row>
@@ -8971,17 +8971,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9088,32 +9088,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>68064</t>
+          <t>67367</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57024</t>
+          <t>55710</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79998</t>
+          <t>80124</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9123,17 +9123,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>95470</t>
+          <t>97953</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>84296</t>
+          <t>85683</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>107811</t>
+          <t>110270</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9158,32 +9158,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>163534</t>
+          <t>165319</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>147611</t>
+          <t>149459</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>180938</t>
+          <t>183735</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,38%</t>
         </is>
       </c>
     </row>
@@ -9201,32 +9201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>201572</t>
+          <t>203340</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>189638</t>
+          <t>190583</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>212612</t>
+          <t>214997</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9236,17 +9236,17 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>161586</t>
+          <t>165797</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>149245</t>
+          <t>153480</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>172760</t>
+          <t>178067</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9271,32 +9271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>363158</t>
+          <t>369138</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>345754</t>
+          <t>350722</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>379081</t>
+          <t>384998</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,04%</t>
         </is>
       </c>
     </row>
@@ -9314,17 +9314,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9349,17 +9349,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9431,32 +9431,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>141257</t>
+          <t>161379</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>118333</t>
+          <t>138449</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>163599</t>
+          <t>185034</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9466,32 +9466,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>282409</t>
+          <t>336234</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>133156</t>
+          <t>310354</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>382248</t>
+          <t>362075</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9501,32 +9501,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>423666</t>
+          <t>497612</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>273716</t>
+          <t>460668</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>506079</t>
+          <t>535187</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -9544,32 +9544,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>483022</t>
+          <t>558308</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>460680</t>
+          <t>534653</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>505946</t>
+          <t>581238</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9579,32 +9579,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>566856</t>
+          <t>435823</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>467017</t>
+          <t>409982</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>716109</t>
+          <t>461703</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9614,32 +9614,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1049878</t>
+          <t>994132</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>967465</t>
+          <t>956557</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1199828</t>
+          <t>1031076</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>69,12%</t>
         </is>
       </c>
     </row>
@@ -9657,17 +9657,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9692,17 +9692,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9727,17 +9727,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9774,32 +9774,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>86479</t>
+          <t>97640</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39547</t>
+          <t>81538</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>124649</t>
+          <t>115209</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9809,32 +9809,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>187603</t>
+          <t>209162</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>169700</t>
+          <t>189396</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>209324</t>
+          <t>230625</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9844,32 +9844,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>274082</t>
+          <t>306802</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>171320</t>
+          <t>280691</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>332537</t>
+          <t>335765</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -9887,32 +9887,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>842241</t>
+          <t>700432</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>804071</t>
+          <t>682863</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>889173</t>
+          <t>716534</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9922,32 +9922,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>530128</t>
+          <t>622169</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>508407</t>
+          <t>600706</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>548031</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9957,32 +9957,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1372370</t>
+          <t>1322601</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1313915</t>
+          <t>1293638</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1475132</t>
+          <t>1348712</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>82,77%</t>
         </is>
       </c>
     </row>
@@ -10000,17 +10000,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10035,17 +10035,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10070,17 +10070,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10117,32 +10117,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>595095</t>
+          <t>640992</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>457566</t>
+          <t>597395</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>659443</t>
+          <t>691624</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10152,32 +10152,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1099603</t>
+          <t>1209415</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>872848</t>
+          <t>1167141</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1194874</t>
+          <t>1265328</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10187,32 +10187,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1694698</t>
+          <t>1850407</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1444766</t>
+          <t>1775947</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1814112</t>
+          <t>1927855</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -10230,32 +10230,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2864722</t>
+          <t>2891770</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2800374</t>
+          <t>2841138</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3002251</t>
+          <t>2935367</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10265,32 +10265,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2612677</t>
+          <t>2527539</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2517406</t>
+          <t>2471626</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2839432</t>
+          <t>2569813</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10300,32 +10300,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5477399</t>
+          <t>5419309</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5357985</t>
+          <t>5341861</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5727331</t>
+          <t>5493769</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>75,57%</t>
         </is>
       </c>
     </row>
@@ -10343,17 +10343,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10378,17 +10378,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10413,17 +10413,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
